--- a/P1278_Config.xlsx
+++ b/P1278_Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\PAS_CONFIG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\PAS_Graphs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419FD15A-9A0D-41DB-B31B-9CDE21D7EB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F8CD9C-182B-4882-94FA-EA6648FCDDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32811" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="2" xr2:uid="{18838EF4-2194-40DC-9B61-2B600CFE03D6}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{18838EF4-2194-40DC-9B61-2B600CFE03D6}"/>
   </bookViews>
   <sheets>
     <sheet name="PlotConfig" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="61">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -989,21 +989,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECA0C86C-E521-43B5-8F9B-EC13228529AF}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.61328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15.23046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.4609375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -1029,9 +1029,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>20</v>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1278</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>40</v>
@@ -1055,9 +1055,9 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>20</v>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1278</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>40</v>
@@ -1081,9 +1081,9 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>20</v>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1278</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>40</v>
@@ -1107,9 +1107,9 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>20</v>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1278</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>8</v>
@@ -1133,9 +1133,9 @@
         <v>45883</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>20</v>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1278</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>8</v>
@@ -1159,9 +1159,9 @@
         <v>45883</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>20</v>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1278</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>8</v>
@@ -1185,9 +1185,9 @@
         <v>45883</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>20</v>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1278</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>21</v>
@@ -1211,9 +1211,9 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>20</v>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1278</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>21</v>
@@ -1237,9 +1237,9 @@
         <v>45994</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>20</v>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1278</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>21</v>
@@ -1263,9 +1263,9 @@
         <v>45991</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>20</v>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1278</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>21</v>
@@ -1289,9 +1289,9 @@
         <v>45981</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>20</v>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1278</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>21</v>
@@ -1315,9 +1315,9 @@
         <v>45981</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>20</v>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1278</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>21</v>
@@ -1341,9 +1341,9 @@
         <v>45985</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>20</v>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>1278</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>21</v>
@@ -1367,9 +1367,9 @@
         <v>45985</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>20</v>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1278</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>21</v>
@@ -1405,21 +1405,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07263D37-FCF4-467F-B5F8-C889C84F79A1}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.61328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15.23046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.4609375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>45873</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>45883</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>45883</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>45883</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>45994</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>45991</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>45981</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>45981</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>45985</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>45985</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1820,12 +1820,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809A96A8-FC28-4758-8695-81635ABD2039}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1841,52 +1841,52 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1904,9 +1904,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB67BBFF-F334-4B66-9D44-66F5AB0D2CC0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>38</v>
       </c>
